--- a/artfynd/A 49858-2025 artfynd.xlsx
+++ b/artfynd/A 49858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89599917</v>
+        <v>89599926</v>
       </c>
       <c r="B2" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382396.8353684352</v>
+        <v>382271</v>
       </c>
       <c r="R2" t="n">
-        <v>7027972.999876656</v>
+        <v>7028014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89599934</v>
+        <v>89599937</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382396.8353684352</v>
+        <v>382397</v>
       </c>
       <c r="R3" t="n">
-        <v>7027972.999876656</v>
+        <v>7027973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89599951</v>
+        <v>89599959</v>
       </c>
       <c r="B4" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382613.1697112281</v>
+        <v>382430</v>
       </c>
       <c r="R4" t="n">
-        <v>7027665.913015389</v>
+        <v>7027851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,21 +945,11 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,11 +958,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sjungande</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1028,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89599959</v>
+        <v>89599934</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>382430.1381302535</v>
+        <v>382397</v>
       </c>
       <c r="R5" t="n">
-        <v>7027850.95118391</v>
+        <v>7027973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1046,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89599937</v>
+        <v>89599917</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>382396.8353684352</v>
+        <v>382397</v>
       </c>
       <c r="R6" t="n">
-        <v>7027972.999876656</v>
+        <v>7027973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1147,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,12 +1183,7 @@
         <v>89599954</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>382215.0971380101</v>
+        <v>382215</v>
       </c>
       <c r="R7" t="n">
-        <v>7028008.870507887</v>
+        <v>7028009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1248,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89599926</v>
+        <v>89599916</v>
       </c>
       <c r="B8" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>382271.056687497</v>
+        <v>382613</v>
       </c>
       <c r="R8" t="n">
-        <v>7028014.000525796</v>
+        <v>7027665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,19 +1349,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,19 +1382,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89599916</v>
+        <v>89599942</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1532,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>382613.1368472942</v>
+        <v>382397</v>
       </c>
       <c r="R9" t="n">
-        <v>7027665.01581577</v>
+        <v>7027973</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,19 +1450,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89599938</v>
+        <v>89599951</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>382613.1697112281</v>
+        <v>382613</v>
       </c>
       <c r="R10" t="n">
-        <v>7027665.913015389</v>
+        <v>7027666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,21 +1551,11 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1704,6 +1564,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sjungande</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1717,238 +1582,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>89599942</v>
-      </c>
-      <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Saumyrhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>382396.8353684352</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7027972.999876656</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>89599950</v>
-      </c>
-      <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Saumyrhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>382396.8353684352</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7027972.999876656</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
